--- a/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0001T0006Z000C1N17_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0001T0006Z000C1N17_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>37.68002518891894</v>
+        <v>6.123004093199328</v>
       </c>
       <c r="D2" t="n">
-        <v>39.29698271435376</v>
+        <v>6.385759691082487</v>
       </c>
       <c r="E2" t="n">
-        <v>7.771312729504708</v>
+        <v>1.262838318544515</v>
       </c>
       <c r="F2" t="n">
-        <v>7.593715632893394</v>
+        <v>1.233978790345177</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>39.87628110725661</v>
+        <v>6.479895679929199</v>
       </c>
       <c r="D3" t="n">
-        <v>39.91850242526738</v>
+        <v>6.486756644105949</v>
       </c>
       <c r="E3" t="n">
-        <v>7.771312729504708</v>
+        <v>1.262838318544515</v>
       </c>
       <c r="F3" t="n">
-        <v>7.593715632893394</v>
+        <v>1.233978790345177</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>35.15295251639343</v>
+        <v>5.712354783913932</v>
       </c>
       <c r="D4" t="n">
-        <v>36.20534725137978</v>
+        <v>5.883368928349214</v>
       </c>
       <c r="E4" t="n">
-        <v>7.771312729504708</v>
+        <v>1.262838318544515</v>
       </c>
       <c r="F4" t="n">
-        <v>7.593715632893394</v>
+        <v>1.233978790345177</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>22.88951154666291</v>
+        <v>3.719545626332722</v>
       </c>
       <c r="D5" t="n">
-        <v>24.24351772257087</v>
+        <v>3.939571629917767</v>
       </c>
       <c r="E5" t="n">
-        <v>7.771312729504708</v>
+        <v>1.262838318544515</v>
       </c>
       <c r="F5" t="n">
-        <v>7.593715632893394</v>
+        <v>1.233978790345177</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>37.79890894790027</v>
+        <v>6.142322704033793</v>
       </c>
       <c r="D6" t="n">
-        <v>36.77223065758503</v>
+        <v>5.975487481857567</v>
       </c>
       <c r="E6" t="n">
-        <v>7.771312729504708</v>
+        <v>1.262838318544515</v>
       </c>
       <c r="F6" t="n">
-        <v>7.593715632893394</v>
+        <v>1.233978790345177</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>25.95108198229647</v>
+        <v>4.217050822123176</v>
       </c>
       <c r="D7" t="n">
-        <v>25.2942895921584</v>
+        <v>4.11032205872574</v>
       </c>
       <c r="E7" t="n">
-        <v>7.771312729504708</v>
+        <v>1.262838318544515</v>
       </c>
       <c r="F7" t="n">
-        <v>7.593715632893394</v>
+        <v>1.233978790345177</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>12.40130249474116</v>
+        <v>2.015211655395438</v>
       </c>
       <c r="D8" t="n">
-        <v>11.36883692646614</v>
+        <v>1.847436000550748</v>
       </c>
       <c r="E8" t="n">
-        <v>7.771312729504708</v>
+        <v>1.262838318544515</v>
       </c>
       <c r="F8" t="n">
-        <v>7.593715632893394</v>
+        <v>1.233978790345177</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>26.35312164242792</v>
+        <v>4.282382266894537</v>
       </c>
       <c r="D9" t="n">
-        <v>28.97513868352571</v>
+        <v>4.708460036072928</v>
       </c>
       <c r="E9" t="n">
-        <v>7.771312729504708</v>
+        <v>1.262838318544515</v>
       </c>
       <c r="F9" t="n">
-        <v>7.593715632893394</v>
+        <v>1.233978790345177</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>39.40579534669987</v>
+        <v>6.403441743838729</v>
       </c>
       <c r="D10" t="n">
-        <v>36.87488349516298</v>
+        <v>5.992168567963984</v>
       </c>
       <c r="E10" t="n">
-        <v>7.771312729504708</v>
+        <v>1.262838318544515</v>
       </c>
       <c r="F10" t="n">
-        <v>7.593715632893394</v>
+        <v>1.233978790345177</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>25.78823406399759</v>
+        <v>4.190588035399609</v>
       </c>
       <c r="D11" t="n">
-        <v>27.48840566219989</v>
+        <v>4.466865920107482</v>
       </c>
       <c r="E11" t="n">
-        <v>7.771312729504708</v>
+        <v>1.262838318544515</v>
       </c>
       <c r="F11" t="n">
-        <v>7.593715632893394</v>
+        <v>1.233978790345177</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>32.23041857637907</v>
+        <v>5.237443018661598</v>
       </c>
       <c r="D12" t="n">
-        <v>29.54885775591501</v>
+        <v>4.801689385336188</v>
       </c>
       <c r="E12" t="n">
-        <v>7.771312729504708</v>
+        <v>1.262838318544515</v>
       </c>
       <c r="F12" t="n">
-        <v>7.593715632893394</v>
+        <v>1.233978790345177</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>35.8811555027177</v>
+        <v>5.830687769191626</v>
       </c>
       <c r="D13" t="n">
-        <v>33.68946955282615</v>
+        <v>5.474538802334249</v>
       </c>
       <c r="E13" t="n">
-        <v>7.771312729504708</v>
+        <v>1.262838318544515</v>
       </c>
       <c r="F13" t="n">
-        <v>7.593715632893394</v>
+        <v>1.233978790345177</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>35.1558310892859</v>
+        <v>5.712822552008959</v>
       </c>
       <c r="D14" t="n">
-        <v>35.1508128136343</v>
+        <v>5.712007082215575</v>
       </c>
       <c r="E14" t="n">
-        <v>7.771312729504708</v>
+        <v>1.262838318544515</v>
       </c>
       <c r="F14" t="n">
-        <v>7.593715632893394</v>
+        <v>1.233978790345177</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
